--- a/Dashboards/data/Data final/empleo/pobreza/pobreza_laboral.xlsx
+++ b/Dashboards/data/Data final/empleo/pobreza/pobreza_laboral.xlsx
@@ -98,10 +98,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>0.46270924806594849</v>
+        <v>0.52768325805664063</v>
       </c>
       <c r="D2" s="1">
-        <v>46.270923614501953</v>
+        <v>52.768325805664063</v>
       </c>
     </row>
     <row r="3">
@@ -112,10 +112,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>0.43828350305557251</v>
+        <v>0.47134321928024292</v>
       </c>
       <c r="D3" s="1">
-        <v>43.828350067138672</v>
+        <v>47.134323120117188</v>
       </c>
     </row>
     <row r="4">
@@ -126,10 +126,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>0.31686320900917053</v>
+        <v>0.36346772313117981</v>
       </c>
       <c r="D4" s="1">
-        <v>31.686321258544922</v>
+        <v>36.346771240234375</v>
       </c>
     </row>
     <row r="5">
@@ -140,10 +140,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>0.25769352912902832</v>
+        <v>0.29574033617973328</v>
       </c>
       <c r="D5" s="1">
-        <v>25.769351959228516</v>
+        <v>29.574033737182617</v>
       </c>
     </row>
     <row r="6">
@@ -154,10 +154,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>0.23556248843669891</v>
+        <v>0.27028539776802063</v>
       </c>
       <c r="D6" s="1">
-        <v>23.556249618530273</v>
+        <v>27.028539657592774</v>
       </c>
     </row>
     <row r="7">
@@ -168,10 +168,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>0.2422480583190918</v>
+        <v>0.28349649906158447</v>
       </c>
       <c r="D7" s="1">
-        <v>24.22480583190918</v>
+        <v>28.349649429321289</v>
       </c>
     </row>
     <row r="8">
@@ -182,10 +182,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>0.2098582535982132</v>
+        <v>0.24948374927043915</v>
       </c>
       <c r="D8" s="1">
-        <v>20.985824584960938</v>
+        <v>24.948375701904297</v>
       </c>
     </row>
     <row r="9">
@@ -196,10 +196,10 @@
         <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>0.18310070037841797</v>
+        <v>0.21348120272159577</v>
       </c>
       <c r="D9" s="1">
-        <v>18.310070037841797</v>
+        <v>21.348119735717773</v>
       </c>
     </row>
     <row r="10">
@@ -210,10 +210,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="1">
-        <v>0.16741535067558289</v>
+        <v>0.20564930140972138</v>
       </c>
       <c r="D10" s="1">
-        <v>16.741535186767578</v>
+        <v>20.564929962158203</v>
       </c>
     </row>
     <row r="11">
@@ -224,10 +224,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>0.15575192868709564</v>
+        <v>0.18078508973121643</v>
       </c>
       <c r="D11" s="1">
-        <v>15.575192451477051</v>
+        <v>18.078508377075195</v>
       </c>
     </row>
     <row r="12">
@@ -238,10 +238,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>0.1357572078704834</v>
+        <v>0.1616663783788681</v>
       </c>
       <c r="D12" s="1">
-        <v>13.57572078704834</v>
+        <v>16.166637420654297</v>
       </c>
     </row>
     <row r="13">
@@ -252,10 +252,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>0.13933205604553223</v>
+        <v>0.17393015325069427</v>
       </c>
       <c r="D13" s="1">
-        <v>13.933205604553223</v>
+        <v>17.393014907836914</v>
       </c>
     </row>
     <row r="14">
@@ -266,10 +266,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>0.14305873215198517</v>
+        <v>0.18051086366176605</v>
       </c>
       <c r="D14" s="1">
-        <v>14.305872917175293</v>
+        <v>18.05108642578125</v>
       </c>
     </row>
     <row r="15">
@@ -280,10 +280,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="1">
-        <v>0.13016360998153687</v>
+        <v>0.16823691129684448</v>
       </c>
       <c r="D15" s="1">
-        <v>13.016361236572266</v>
+        <v>16.823690414428711</v>
       </c>
     </row>
     <row r="16">
@@ -294,10 +294,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="1">
-        <v>0.13984054327011108</v>
+        <v>0.23241600394248963</v>
       </c>
       <c r="D16" s="1">
-        <v>13.984054565429688</v>
+        <v>23.241600036621094</v>
       </c>
     </row>
     <row r="17">
@@ -308,10 +308,10 @@
         <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>0.15126381814479828</v>
+        <v>0.19861707091331482</v>
       </c>
       <c r="D17" s="1">
-        <v>15.126381874084473</v>
+        <v>19.86170768737793</v>
       </c>
     </row>
     <row r="18">
@@ -322,10 +322,10 @@
         <v>2</v>
       </c>
       <c r="C18" s="1">
-        <v>0.20836442708969116</v>
+        <v>0.26170995831489563</v>
       </c>
       <c r="D18" s="1">
-        <v>20.836442947387695</v>
+        <v>26.170995712280273</v>
       </c>
     </row>
     <row r="19">
@@ -336,10 +336,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>0.18738487362861633</v>
+        <v>0.22321628034114838</v>
       </c>
       <c r="D19" s="1">
-        <v>18.738487243652344</v>
+        <v>22.321628570556641</v>
       </c>
     </row>
     <row r="20">
@@ -350,10 +350,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>0.1583293080329895</v>
+        <v>0.19548998773097992</v>
       </c>
       <c r="D20" s="1">
-        <v>15.832930564880371</v>
+        <v>19.54899787902832</v>
       </c>
     </row>
     <row r="21">
@@ -364,10 +364,10 @@
         <v>2</v>
       </c>
       <c r="C21" s="1">
-        <v>0.16080851852893829</v>
+        <v>0.19752660393714905</v>
       </c>
       <c r="D21" s="1">
-        <v>16.080852508544922</v>
+        <v>19.752660751342774</v>
       </c>
     </row>
     <row r="22">
@@ -378,10 +378,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="1">
-        <v>0.16860856115818024</v>
+        <v>0.21064116060733795</v>
       </c>
       <c r="D22" s="1">
-        <v>16.860857009887695</v>
+        <v>21.064115524291992</v>
       </c>
     </row>
     <row r="23">
@@ -392,10 +392,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="1">
-        <v>0.14320676028728485</v>
+        <v>0.169438436627388</v>
       </c>
       <c r="D23" s="1">
-        <v>14.320675849914551</v>
+        <v>16.943843841552734</v>
       </c>
     </row>
   </sheetData>
